--- a/ru/downloads/data-excel/4.c.1.xlsx
+++ b/ru/downloads/data-excel/4.c.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB690F2-5C37-4455-9C41-631B79AB8437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -73,7 +74,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -161,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -187,15 +188,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -214,9 +216,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -254,9 +256,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -291,7 +293,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -326,7 +328,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -499,15 +501,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="36" style="4" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
@@ -518,7 +520,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -529,7 +531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="2"/>
       <c r="C3" s="6"/>
@@ -547,8 +549,9 @@
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
+      <c r="R3" s="15"/>
     </row>
-    <row r="4" spans="1:17" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
@@ -600,8 +603,11 @@
       <c r="Q4" s="10">
         <v>2023</v>
       </c>
+      <c r="R4" s="15">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -614,10 +620,10 @@
       <c r="D5" s="11">
         <v>87.9</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="11">
         <v>89.6</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="11">
         <v>87.5</v>
       </c>
       <c r="G5" s="11">
@@ -653,8 +659,11 @@
       <c r="Q5" s="11">
         <v>93.7</v>
       </c>
+      <c r="R5" s="14">
+        <v>93.1</v>
+      </c>
     </row>
-    <row r="6" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
@@ -667,10 +676,10 @@
       <c r="D6" s="11">
         <v>93.6</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="11">
         <v>93.3</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="11">
         <v>93.9</v>
       </c>
       <c r="G6" s="11">
@@ -700,14 +709,17 @@
       <c r="O6" s="11">
         <v>96.6</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P6" s="13">
         <v>96</v>
       </c>
-      <c r="Q6" s="14">
+      <c r="Q6" s="13">
         <v>95.5</v>
       </c>
+      <c r="R6" s="14">
+        <v>95.7</v>
+      </c>
     </row>
-    <row r="7" spans="1:17" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -720,10 +732,10 @@
       <c r="D7" s="12">
         <v>92.9</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="12">
         <v>92.8</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="12">
         <v>94.1</v>
       </c>
       <c r="G7" s="12">
@@ -759,8 +771,11 @@
       <c r="Q7" s="12">
         <v>97.1</v>
       </c>
+      <c r="R7" s="16">
+        <v>97</v>
+      </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="L8" s="9"/>
     </row>
   </sheetData>
